--- a/example data/25mm/Results/ID 14 - Run 3/ID 14 - Run 3 - Standard Devs. Stepcycle.xlsx
+++ b/example data/25mm/Results/ID 14 - Run 3/ID 14 - Run 3 - Standard Devs. Stepcycle.xlsx
@@ -425,181 +425,256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AX26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SC Percentages</t>
+          <t>SC Percentage</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Nose x</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Nose y</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ear base x</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ear base y</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Front paw tao x</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Front paw tao y</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Wrist x</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Wrist y</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Elbow x</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Elbow y</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Lower Shoulder x</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Lower Shoulder y</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Upper Shoulder x</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Upper Shoulder y</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest x</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Iliac Crest y</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Hip x</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Hip y</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Knee x</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Knee y</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle x</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Ankle y</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao x</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Hind paw tao y</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tail base x</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Tail base y</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tail center x</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Tail center y</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tail tip x</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Tail tip y</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao Velocity</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Hind paw tao Acceleration</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Velocity</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Ankle Acceleration</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Velocity</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Knee Acceleration</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Velocity</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Hip Acceleration</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Velocity</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Iliac Crest Acceleration</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Velocity</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Hind paw tao Acceleration</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Velocity</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Ankle Acceleration</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Velocity</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Knee Acceleration</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Velocity</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Hip Acceleration</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Velocity</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Iliac Crest Acceleration</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle Velocity</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Ankle Angle Acceleration</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle Velocity</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Knee Angle Acceleration</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle Velocity</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Hip Angle Acceleration</t>
         </is>
@@ -610,106 +685,151 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2309058228000544</v>
+        <v>0.3617011782851443</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4237895007697329</v>
+        <v>0.2309058228000532</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3771800404181576</v>
+        <v>0.9099670877022777</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5348465429752886</v>
+        <v>0.4237895007697325</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6873647414644335</v>
+        <v>2.512010606146598</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5191603733791863</v>
+        <v>0.3771800404181593</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4742231105058817</v>
+        <v>1.867017120404652</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5897859405101714</v>
+        <v>0.5348465429752929</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7857129530972896</v>
+        <v>0.8149404602253472</v>
       </c>
       <c r="K2" t="n">
-        <v>1.293271263327383</v>
+        <v>0.6873647414644334</v>
       </c>
       <c r="L2" t="n">
-        <v>1.044546288438275</v>
+        <v>0.92051650390937</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4576114535355043</v>
+        <v>0.5191603733791788</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8235250385939225</v>
+        <v>0.7422668268103525</v>
       </c>
       <c r="O2" t="n">
-        <v>1.624940905865138</v>
+        <v>0.4742231105058833</v>
       </c>
       <c r="P2" t="n">
-        <v>3.527014762309452</v>
+        <v>1.037927147725269</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.39511090652197</v>
+        <v>0.5897859405101691</v>
       </c>
       <c r="R2" t="n">
-        <v>4.279052565835771</v>
+        <v>0.6514163652400995</v>
       </c>
       <c r="S2" t="n">
-        <v>5.240479064123532</v>
+        <v>0.7857129530972903</v>
       </c>
       <c r="T2" t="n">
+        <v>1.107196926376193</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.293271263327379</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.9938046248594867</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.044546288438274</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.12093795044047</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.4576114535355049</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.9332122994018733</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.8235250385939268</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.521663512564448</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.624940905865139</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.552836016451612</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3.52701476230945</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.008021115120044</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AG2" t="n">
         <v>0.6704832548134129</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AH2" t="n">
         <v>0.5153478823822918</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AI2" t="n">
         <v>0.2458491840900711</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AJ2" t="n">
         <v>0.5386753774108356</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AK2" t="n">
         <v>0.5804338839050146</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AL2" t="n">
         <v>0.548566635603844</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AM2" t="n">
         <v>0.531127211552519</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AN2" t="n">
         <v>0.4259518119809388</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AO2" t="n">
         <v>0.5866862018457206</v>
       </c>
-      <c r="AD2" t="n">
-        <v>3.431300151860821</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.81876360297534</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>3.924176617614607</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.752079528892263</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>3.93104392047408</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3.014737488135025</v>
+      <c r="AP2" t="n">
+        <v>11.39511090652196</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4.279052565835774</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5.240479064123506</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.431300151860825</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.818763602975338</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.924176617614633</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.752079528892306</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3.931043920474088</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.014737488135021</v>
       </c>
     </row>
     <row r="3">
@@ -717,106 +837,151 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.366410239330389</v>
+        <v>1.384028815156791</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2148805819024447</v>
+        <v>0.3664102393303869</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2606858252145665</v>
+        <v>0.6526923165659473</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5728805608377564</v>
+        <v>0.2148805819024527</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7605589250677542</v>
+        <v>2.434346981180735</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4213927094948115</v>
+        <v>0.2606858252145666</v>
       </c>
       <c r="H3" t="n">
-        <v>0.416180812459367</v>
+        <v>1.827399617192141</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4102991877624866</v>
+        <v>0.5728805608377595</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6817371206136432</v>
+        <v>0.5024573900133853</v>
       </c>
       <c r="K3" t="n">
-        <v>1.60372037817639</v>
+        <v>0.7605589250677547</v>
       </c>
       <c r="L3" t="n">
-        <v>1.343679056165493</v>
+        <v>0.6068693849573638</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8649631888757957</v>
+        <v>0.4213927094948105</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6147092455357936</v>
+        <v>0.7768714842279311</v>
       </c>
       <c r="O3" t="n">
+        <v>0.4161808124593713</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8072807200004847</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.4102991877624955</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.20848945841861</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.6817371206136466</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6525875844735193</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.603720378176397</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.145098110131836</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.343679056165487</v>
+      </c>
+      <c r="X3" t="n">
+        <v>5.97675290266152</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.8649631888757866</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.759037966030656</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.614709245535799</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.379082904610909</v>
+      </c>
+      <c r="AC3" t="n">
         <v>1.85807329008118</v>
       </c>
-      <c r="P3" t="n">
-        <v>3.773119083542012</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>18.84253163114709</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.612517259354733</v>
-      </c>
-      <c r="S3" t="n">
-        <v>8.295417550663148</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="AD3" t="n">
+        <v>4.592500351597101</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3.773119083542015</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0.7486792636456231</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AG3" t="n">
         <v>0.4352807880191244</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AH3" t="n">
         <v>0.4366018074172444</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AI3" t="n">
         <v>0.2187689448760375</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AJ3" t="n">
         <v>0.3242495272906631</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AK3" t="n">
         <v>0.418468246384847</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AL3" t="n">
         <v>0.3691834270745404</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AM3" t="n">
         <v>0.4395884506878177</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AN3" t="n">
         <v>0.5026054138502174</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AO3" t="n">
         <v>0.3012316667073922</v>
       </c>
-      <c r="AD3" t="n">
-        <v>5.63033147829408</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.117347242605099</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>4.49941239989358</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.8468515516423096</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>3.825298659218058</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>4.48200433918352</v>
+      <c r="AP3" t="n">
+        <v>18.84253163114708</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2.612517259354755</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8.295417550663169</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.630331478294072</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.117347242605097</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.499412399893552</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.8468515516423265</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>3.82529865921804</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.482004339183529</v>
       </c>
     </row>
     <row r="4">
@@ -824,106 +989,151 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6363980886987406</v>
+        <v>2.002042206378672</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2563955000550566</v>
+        <v>0.6363980886987376</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1456110244492553</v>
+        <v>0.9963483492741024</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6412556020268479</v>
+        <v>0.2563955000550542</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4831581074699138</v>
+        <v>2.335332347963582</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1819844963559327</v>
+        <v>0.145611024449252</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1916328233774007</v>
+        <v>1.898747728571175</v>
       </c>
       <c r="I4" t="n">
-        <v>0.674173440072772</v>
+        <v>0.6412556020268504</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3947322395743629</v>
+        <v>0.8782152242501611</v>
       </c>
       <c r="K4" t="n">
-        <v>1.294164221658672</v>
+        <v>0.4831581074699146</v>
       </c>
       <c r="L4" t="n">
-        <v>2.391196766731719</v>
+        <v>0.7900053453151232</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7083365454184418</v>
+        <v>0.1819844963559286</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8172806919403289</v>
+        <v>1.297683154415392</v>
       </c>
       <c r="O4" t="n">
-        <v>2.280067644503272</v>
+        <v>0.1916328233773961</v>
       </c>
       <c r="P4" t="n">
-        <v>5.370898321405284</v>
+        <v>1.588824548784748</v>
       </c>
       <c r="Q4" t="n">
+        <v>0.6741734400727721</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.383688593653546</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.3947322395743543</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.683730120639545</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.294164221658671</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2.602642761914455</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.391196766731724</v>
+      </c>
+      <c r="X4" t="n">
+        <v>7.326724225386458</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.708336545418444</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.028110423924586</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.8172806919403367</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3.078536345545022</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.280067644503275</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>5.149331148175986</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>5.370898321405289</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.090181427451202</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.5003433994356694</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.3411049751250047</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.3982335007953764</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2145541621056291</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.21326968580329</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.2839215065517454</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.3130817775958656</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.111657145206735</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.2923023324830437</v>
+      </c>
+      <c r="AP4" t="n">
         <v>15.79374224178694</v>
       </c>
-      <c r="R4" t="n">
-        <v>11.2875611749537</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8.732786711617377</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.090181427451202</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.5003433994356694</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.3411049751250047</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.3982335007953764</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.2145541621056291</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.21326968580329</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.2839215065517454</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.3130817775958656</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.111657145206735</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.2923023324830437</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>6.348853485714195</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.167621167548948</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>4.682164801838295</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.109368682765867</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>3.932991489208182</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>4.082480436186745</v>
+      <c r="AQ4" t="n">
+        <v>11.28756117495368</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>8.73278671161736</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6.348853485714203</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.16762116754894</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.682164801838317</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.10936868276585</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.932991489208217</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.082480436186737</v>
       </c>
     </row>
     <row r="5">
@@ -931,106 +1141,151 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5403141199361225</v>
+        <v>2.352148291452465</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3083677378379017</v>
+        <v>0.5403141199361214</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3120663482617292</v>
+        <v>1.431514490855576</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5316845698904108</v>
+        <v>0.3083677378379039</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3511104472954925</v>
+        <v>2.12523956347879</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2865234045445505</v>
+        <v>0.3120663482617251</v>
       </c>
       <c r="H5" t="n">
-        <v>0.327974544114803</v>
+        <v>1.651616735676832</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7456057289984354</v>
+        <v>0.5316845698904057</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3682107882810078</v>
+        <v>1.296168561731359</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9424293442801874</v>
+        <v>0.3511104472954901</v>
       </c>
       <c r="L5" t="n">
-        <v>3.376836492278735</v>
+        <v>1.045624782015761</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6201744454649644</v>
+        <v>0.2865234045445511</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9260566918208911</v>
+        <v>1.571844904756383</v>
       </c>
       <c r="O5" t="n">
-        <v>2.44903327800407</v>
+        <v>0.3279745441148048</v>
       </c>
       <c r="P5" t="n">
-        <v>5.734808599656206</v>
+        <v>1.991703120886396</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.750381879699006</v>
+        <v>0.7456057289984401</v>
       </c>
       <c r="R5" t="n">
-        <v>19.08046323156839</v>
+        <v>1.998949670229307</v>
       </c>
       <c r="S5" t="n">
-        <v>6.228790311361643</v>
+        <v>0.3682107882810061</v>
       </c>
       <c r="T5" t="n">
+        <v>2.172235732163523</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.9424293442801975</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4.326269778517899</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.376836492278732</v>
+      </c>
+      <c r="X5" t="n">
+        <v>7.595262696192175</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.620174445464973</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.158823603623737</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.9260566918208932</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.69091555746816</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.449033278004074</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>5.945422855857838</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>5.73480859965621</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.467001156464641</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AG5" t="n">
         <v>0.5483640453160327</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AH5" t="n">
         <v>0.7262686446018161</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AI5" t="n">
         <v>0.557761641903162</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AJ5" t="n">
         <v>0.1834268987910974</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AK5" t="n">
         <v>0.08242874149036281</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AL5" t="n">
         <v>0.2917959543031582</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AM5" t="n">
         <v>0.1287412130087742</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AN5" t="n">
         <v>0.3528236951651413</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AO5" t="n">
         <v>0.1606582081352418</v>
       </c>
-      <c r="AD5" t="n">
-        <v>6.811367763283633</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.31931812265285</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>3.463736607046522</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.90657361506676</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>3.708909288902581</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>2.420825690388369</v>
+      <c r="AP5" t="n">
+        <v>8.750381879698988</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>19.08046323156843</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6.228790311361662</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6.81136776328364</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.319318122652847</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.463736607046494</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.906573615066781</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3.708909288902558</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>2.420825690388392</v>
       </c>
     </row>
     <row r="6">
@@ -1038,106 +1293,151 @@
         <v>20</v>
       </c>
       <c r="B6" t="n">
-        <v>1.065521085426063</v>
+        <v>2.554566763121216</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7218009802155262</v>
+        <v>1.065521085426054</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2356435938845293</v>
+        <v>1.701873389993094</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6409329903221747</v>
+        <v>0.7218009802155242</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2426827762019534</v>
+        <v>1.922681666339064</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5657991801818857</v>
+        <v>0.2356435938845331</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7175062444381869</v>
+        <v>1.391570297753218</v>
       </c>
       <c r="I6" t="n">
-        <v>1.010862437244114</v>
+        <v>0.6409329903221812</v>
       </c>
       <c r="J6" t="n">
+        <v>1.082093226409732</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2426827762019469</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.071558679316278</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5657991801818736</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.859265375506403</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.7175062444381821</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.261742738166222</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.01086243724411</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.253583268289389</v>
+      </c>
+      <c r="S6" t="n">
         <v>0.2512051002870243</v>
       </c>
-      <c r="K6" t="n">
-        <v>0.5961757206433893</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="T6" t="n">
+        <v>3.563153977481065</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.5961757206433899</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.47595854435118</v>
+      </c>
+      <c r="W6" t="n">
         <v>3.137831086351214</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.86632633231334</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.8737287034678417</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.36692246819126</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5.265172641272014</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.354127314456468</v>
-      </c>
-      <c r="R6" t="n">
-        <v>22.52370546344495</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.23038459575186</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="X6" t="n">
+        <v>7.952025342223672</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.8663263323133412</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.091102240308914</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.8737287034678436</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4.45406869807686</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.366922468191266</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>6.590433255508283</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>5.26517264127202</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2.522056452898886</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AG6" t="n">
         <v>0.4655897780904837</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AH6" t="n">
         <v>1.74146021653253</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AI6" t="n">
         <v>0.8369543305363902</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AJ6" t="n">
         <v>0.686506548530271</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AK6" t="n">
         <v>0.2662484358652659</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AL6" t="n">
         <v>0.656793683967679</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AM6" t="n">
         <v>0.2837693538734791</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AN6" t="n">
         <v>0.4667470330016562</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AO6" t="n">
         <v>0.396662831252605</v>
       </c>
-      <c r="AD6" t="n">
-        <v>8.229053871908036</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.670531245348401</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>6.403473770869446</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4.461596283607971</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.644158337344169</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.744271721593506</v>
+      <c r="AP6" t="n">
+        <v>3.354127314456481</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>22.52370546344496</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.230384595751871</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8.229053871908015</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.670531245348404</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.403473770869438</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.461596283607975</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.644158337344168</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.744271721593493</v>
       </c>
     </row>
     <row r="7">
@@ -1145,106 +1445,151 @@
         <v>24</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9195872905018193</v>
+        <v>2.532342368917434</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6217675930291215</v>
+        <v>0.9195872905018126</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3011465302929554</v>
+        <v>2.018842882117664</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7101475193238607</v>
+        <v>0.621767593029117</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2978974580800253</v>
+        <v>1.818196230769376</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4274370703082859</v>
+        <v>0.3011465302929519</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5881445618640945</v>
+        <v>1.192835077502922</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9755323935895303</v>
+        <v>0.7101475193238584</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1397053624627713</v>
+        <v>1.433533826778684</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6204119751769349</v>
+        <v>0.2978974580800167</v>
       </c>
       <c r="L7" t="n">
-        <v>2.033855768862798</v>
+        <v>1.417541527659102</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4287395266754837</v>
+        <v>0.4274370703082863</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9850880926834107</v>
+        <v>2.092838388686756</v>
       </c>
       <c r="O7" t="n">
-        <v>1.789013481733474</v>
+        <v>0.5881445618640877</v>
       </c>
       <c r="P7" t="n">
-        <v>4.277262379919265</v>
+        <v>3.966372361916924</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.99000013570734</v>
+        <v>0.9755323935895351</v>
       </c>
       <c r="R7" t="n">
-        <v>17.81225300110011</v>
+        <v>3.947610341963156</v>
       </c>
       <c r="S7" t="n">
-        <v>3.517440458976906</v>
+        <v>0.1397053624627684</v>
       </c>
       <c r="T7" t="n">
+        <v>4.162888307507797</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.6204119751769317</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.442258758831518</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.033855768862805</v>
+      </c>
+      <c r="X7" t="n">
+        <v>7.449375654736456</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.4287395266754873</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.485945633236713</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.9850880926834157</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>5.02763486447971</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.789013481733478</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>7.09099002294186</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>4.277262379919267</v>
+      </c>
+      <c r="AF7" t="n">
         <v>2.736700415536852</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AG7" t="n">
         <v>1.03823152861883</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AH7" t="n">
         <v>1.807445539469966</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AI7" t="n">
         <v>1.341533718413646</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AJ7" t="n">
         <v>0.8581953340896475</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AK7" t="n">
         <v>0.5039490858016268</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AL7" t="n">
         <v>0.6767879433606384</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AM7" t="n">
         <v>0.4183093506853536</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AN7" t="n">
         <v>0.7696139195115227</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AO7" t="n">
         <v>0.5112421031171928</v>
       </c>
-      <c r="AD7" t="n">
-        <v>3.601098176506605</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>5.020609035557169</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>6.996607133437907</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.858604071221912</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.330524387019593</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.286991618779963</v>
+      <c r="AP7" t="n">
+        <v>10.99000013570731</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>17.81225300110013</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.51744045897694</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.601098176506615</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.020609035557164</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.996607133437926</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.858604071221907</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.330524387019572</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.286991618779975</v>
       </c>
     </row>
     <row r="8">
@@ -1252,106 +1597,151 @@
         <v>28</v>
       </c>
       <c r="B8" t="n">
-        <v>1.047228677815002</v>
+        <v>2.57648945849255</v>
       </c>
       <c r="C8" t="n">
+        <v>1.047228677815004</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.051512336950632</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.5430050426431698</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.6530127651481924</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.088392480933233</v>
-      </c>
       <c r="F8" t="n">
-        <v>0.7347332090077037</v>
+        <v>1.784211238954996</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3431632798250067</v>
+        <v>0.6530127651482042</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5542164293749103</v>
+        <v>1.667937265596708</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4108637101432126</v>
+        <v>1.08839248093324</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3044604593834662</v>
+        <v>2.009762323282493</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2832464072106775</v>
+        <v>0.7347332090077116</v>
       </c>
       <c r="L8" t="n">
-        <v>1.171726947902161</v>
+        <v>1.91908613597193</v>
       </c>
       <c r="M8" t="n">
-        <v>0.801555638229612</v>
+        <v>0.3431632798250042</v>
       </c>
       <c r="N8" t="n">
+        <v>2.537064068618461</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5542164293749055</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.399007779462688</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4108637101432177</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.389920756227655</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.304460459383464</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.632923072445278</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.2832464072106715</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.280461075733844</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.171726947902158</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.836772624818434</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.801555638229608</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.392801986906974</v>
+      </c>
+      <c r="AA8" t="n">
         <v>1.17527389706648</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.342262584985719</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3.364294809461624</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>9.780394585717314</v>
-      </c>
-      <c r="R8" t="n">
-        <v>10.23952531649694</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.634774989200774</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="AB8" t="n">
+        <v>4.435102405284035</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.342262584985728</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>6.794025855270199</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3.364294809461628</v>
+      </c>
+      <c r="AF8" t="n">
         <v>3.105611110702496</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AG8" t="n">
         <v>0.2440172225758209</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AH8" t="n">
         <v>2.576136959071265</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AI8" t="n">
         <v>0.3753338235028965</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AJ8" t="n">
         <v>1.002354332071507</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AK8" t="n">
         <v>0.1210044125645324</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AL8" t="n">
         <v>0.7049127837081154</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AM8" t="n">
         <v>0.131436538462261</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AN8" t="n">
         <v>0.814333652283368</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AO8" t="n">
         <v>0.1536284673433152</v>
       </c>
-      <c r="AD8" t="n">
-        <v>1.953622150771622</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>3.527195372305351</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>7.896575232523823</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.9548193089575173</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.346046053540805</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.661117388353764</v>
+      <c r="AP8" t="n">
+        <v>9.780394585717293</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10.23952531649693</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.634774989200761</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.953622150771635</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.527195372305347</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.896575232523797</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.9548193089575082</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.346046053540824</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.661117388353747</v>
       </c>
     </row>
     <row r="9">
@@ -1359,106 +1749,151 @@
         <v>32</v>
       </c>
       <c r="B9" t="n">
-        <v>1.120471272502609</v>
+        <v>2.51705417395568</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5527896260848459</v>
+        <v>1.120471272502599</v>
       </c>
       <c r="D9" t="n">
+        <v>1.843737332864272</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5527896260848428</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.310618936868158</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.048136894252727</v>
       </c>
-      <c r="E9" t="n">
-        <v>1.179775960340606</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.252764767079071</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.5709201531784245</v>
-      </c>
       <c r="H9" t="n">
-        <v>0.6802792952935947</v>
+        <v>3.695573809209638</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2606658520413805</v>
+        <v>1.179775960340607</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2508707330964915</v>
+        <v>2.277732545769776</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3276341251675237</v>
+        <v>1.252764767079061</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6574056028331154</v>
+        <v>2.05868113509404</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09278743205849</v>
+        <v>0.5709201531784165</v>
       </c>
       <c r="N9" t="n">
-        <v>1.023885946296894</v>
+        <v>2.381813060524872</v>
       </c>
       <c r="O9" t="n">
-        <v>1.397491491147927</v>
+        <v>0.680279295293597</v>
       </c>
       <c r="P9" t="n">
-        <v>3.230808251779613</v>
+        <v>2.8389089469201</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.51537719262539</v>
+        <v>0.2606658520413725</v>
       </c>
       <c r="R9" t="n">
-        <v>4.486352818132266</v>
+        <v>3.196500644285083</v>
       </c>
       <c r="S9" t="n">
-        <v>2.139707059134764</v>
+        <v>0.2508707330964842</v>
       </c>
       <c r="T9" t="n">
+        <v>3.029200888222016</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.3276341251675161</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.949225262434461</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.6574056028331111</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.341817014101791</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.092787432058479</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.978973841246268</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.023885946296899</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.972811265206578</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.397491491147937</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>5.985972012338041</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3.230808251779615</v>
+      </c>
+      <c r="AF9" t="n">
         <v>2.398854045894435</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AG9" t="n">
         <v>0.9313799139978285</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AH9" t="n">
         <v>2.348734372090421</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AI9" t="n">
         <v>0.5468662293446234</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AJ9" t="n">
         <v>0.9739989178735246</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AK9" t="n">
         <v>0.1184235932801048</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AL9" t="n">
         <v>0.9625717170416218</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AM9" t="n">
         <v>0.2192150095730896</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AN9" t="n">
         <v>0.9172661989880463</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AO9" t="n">
         <v>0.2354873593728824</v>
       </c>
-      <c r="AD9" t="n">
-        <v>4.34598771333956</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.661531368017378</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>7.788922443363692</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.465870038182181</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>2.159993792293659</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.878928854062284</v>
+      <c r="AP9" t="n">
+        <v>7.515377192625352</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4.486352818132302</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.139707059134813</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.345987713339534</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.66153136801737</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.788922443363663</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.465870038182158</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.159993792293647</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.878928854062289</v>
       </c>
     </row>
     <row r="10">
@@ -1466,106 +1901,151 @@
         <v>36</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6757695984853362</v>
+        <v>2.314020867983575</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3361607191545011</v>
+        <v>0.6757695984853421</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6634665840278897</v>
+        <v>1.756425051817044</v>
       </c>
       <c r="E10" t="n">
-        <v>1.250045229138722</v>
+        <v>0.3361607191544981</v>
       </c>
       <c r="F10" t="n">
-        <v>1.156698601235978</v>
+        <v>3.97435247571858</v>
       </c>
       <c r="G10" t="n">
-        <v>0.453686149697632</v>
+        <v>0.6634665840278995</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2366992691924793</v>
+        <v>6.137402345179039</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5462611882575992</v>
+        <v>1.250045229138717</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2621629548944963</v>
+        <v>2.527160989708613</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6601040644560965</v>
+        <v>1.156698601235974</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7938341455599081</v>
+        <v>2.237419875175382</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9650110228184623</v>
+        <v>0.4536861496976313</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9727285207382884</v>
+        <v>2.422662680090794</v>
       </c>
       <c r="O10" t="n">
-        <v>1.524031376604593</v>
+        <v>0.2366992691924693</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7352448060693</v>
+        <v>2.477478311093007</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.15824809182214</v>
+        <v>0.5462611882576082</v>
       </c>
       <c r="R10" t="n">
-        <v>7.684444108852533</v>
+        <v>2.515378032814656</v>
       </c>
       <c r="S10" t="n">
-        <v>3.47169933659741</v>
+        <v>0.2621629548944989</v>
       </c>
       <c r="T10" t="n">
+        <v>2.779408433959564</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.660104064456099</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3.769998119808289</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.7938341455598905</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.031229055541181</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.9650110228184607</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.501454635591236</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.9727285207382869</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.193142495228397</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.52403137660459</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5.267648586073967</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.735244806069293</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.425311288647646</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AG10" t="n">
         <v>0.9469414846798548</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AH10" t="n">
         <v>1.487410883631677</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AI10" t="n">
         <v>0.9374410008413764</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AJ10" t="n">
         <v>0.808082816901485</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AK10" t="n">
         <v>0.1296354077342823</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AL10" t="n">
         <v>0.9555297014573059</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AM10" t="n">
         <v>0.2712917044680467</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AN10" t="n">
         <v>0.7952029933619336</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AO10" t="n">
         <v>0.2363225387419343</v>
       </c>
-      <c r="AD10" t="n">
-        <v>5.242422759196498</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.622847948879006</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>3.558199619780199</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4.499029814625612</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.994918075679602</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.207735246689059</v>
+      <c r="AP10" t="n">
+        <v>5.158248091822113</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>7.684444108852508</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.471699336597407</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.242422759196486</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.622847948878983</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.558199619780218</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.499029814625588</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.994918075679594</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.20773524668906</v>
       </c>
     </row>
     <row r="11">
@@ -1573,106 +2053,151 @@
         <v>40</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7420930660250021</v>
+        <v>2.16052801967427</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3861669176521942</v>
+        <v>0.7420930660250025</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7897564636877807</v>
+        <v>1.554393742865182</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9954432904564887</v>
+        <v>0.3861669176522004</v>
       </c>
       <c r="F11" t="n">
-        <v>0.871751118713979</v>
+        <v>6.20816165403013</v>
       </c>
       <c r="G11" t="n">
-        <v>0.562785287430589</v>
+        <v>0.7897564636877841</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1580313926903816</v>
+        <v>8.139014902621961</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6890552619310601</v>
+        <v>0.9954432904564806</v>
       </c>
       <c r="J11" t="n">
-        <v>0.242874944006537</v>
+        <v>2.989641836887593</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8087579354566107</v>
+        <v>0.8717511187139739</v>
       </c>
       <c r="L11" t="n">
-        <v>0.970569043534135</v>
+        <v>2.130337525837822</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4796246423606601</v>
+        <v>0.5627852874305936</v>
       </c>
       <c r="N11" t="n">
-        <v>1.140947243163788</v>
+        <v>2.178604193463265</v>
       </c>
       <c r="O11" t="n">
-        <v>1.706475618877379</v>
+        <v>0.1580313926903886</v>
       </c>
       <c r="P11" t="n">
-        <v>4.141669515008588</v>
+        <v>2.294259456733756</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.509304381815876</v>
+        <v>0.6890552619310655</v>
       </c>
       <c r="R11" t="n">
-        <v>7.855998486069003</v>
+        <v>2.275450197993977</v>
       </c>
       <c r="S11" t="n">
-        <v>3.936334211979873</v>
+        <v>0.2428749440065384</v>
       </c>
       <c r="T11" t="n">
+        <v>2.749000894026114</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.8087579354566149</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.175411873865155</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.9705690435341321</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.841998223613904</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4796246423606479</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.007553332282423</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.140947243163785</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.593597178615659</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.706475618877375</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4.741913549695543</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4.141669515008579</v>
+      </c>
+      <c r="AF11" t="n">
         <v>0.581495438279007</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AG11" t="n">
         <v>0.7662107161730519</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AH11" t="n">
         <v>0.4995267715471186</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AI11" t="n">
         <v>0.7239391038704304</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AJ11" t="n">
         <v>0.7348861594967491</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AK11" t="n">
         <v>0.1777626269023109</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AL11" t="n">
         <v>0.5278223949744605</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AM11" t="n">
         <v>0.2915055806987412</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AN11" t="n">
         <v>0.5231492339495074</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AO11" t="n">
         <v>0.2378880255403343</v>
       </c>
-      <c r="AD11" t="n">
-        <v>1.705727789149444</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>3.729883813452194</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.308902119155652</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.560834623312018</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.354462485441571</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.68367030256479</v>
+      <c r="AP11" t="n">
+        <v>7.509304381815852</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>7.85599848606903</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>3.936334211979862</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.705727789149461</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.729883813452201</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.308902119155642</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.56083462331202</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.3544624854415797</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.683670302564771</v>
       </c>
     </row>
     <row r="12">
@@ -1680,106 +2205,151 @@
         <v>44</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8715289151664654</v>
+        <v>1.891238426185078</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4316293817532089</v>
+        <v>0.8715289151664644</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9666858225938941</v>
+        <v>1.351581519341408</v>
       </c>
       <c r="E12" t="n">
-        <v>1.216248574038451</v>
+        <v>0.4316293817532067</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7080299682012323</v>
+        <v>9.097999441349229</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7042132551256189</v>
+        <v>0.9666858225938949</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3422736306674785</v>
+        <v>8.991034396470743</v>
       </c>
       <c r="I12" t="n">
-        <v>0.651147348958125</v>
+        <v>1.21624857403845</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4816743561054703</v>
+        <v>2.189049215098236</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6701345982938278</v>
+        <v>0.7080299682012315</v>
       </c>
       <c r="L12" t="n">
-        <v>1.070750103152947</v>
+        <v>1.732104471472394</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4551207253489503</v>
+        <v>0.7042132551256202</v>
       </c>
       <c r="N12" t="n">
-        <v>1.057881351700487</v>
+        <v>1.720433922186805</v>
       </c>
       <c r="O12" t="n">
-        <v>1.823208104330611</v>
+        <v>0.3422736306674721</v>
       </c>
       <c r="P12" t="n">
-        <v>4.277679017393052</v>
+        <v>2.168339445031755</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.641320305893757</v>
+        <v>0.6511473489581092</v>
       </c>
       <c r="R12" t="n">
-        <v>6.377063590008555</v>
+        <v>2.233136453839699</v>
       </c>
       <c r="S12" t="n">
-        <v>3.615606305253536</v>
+        <v>0.4816743561054575</v>
       </c>
       <c r="T12" t="n">
+        <v>2.810319384705574</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.6701345982938182</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.173000558186585</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.070750103152941</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4.965678102192975</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4551207253489395</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.688223575535753</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.057881351700485</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.25701433183142</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.823208104330606</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.391916583321943</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4.277679017393053</v>
+      </c>
+      <c r="AF12" t="n">
         <v>0.1632416074766619</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AG12" t="n">
         <v>0.3140316833161899</v>
       </c>
-      <c r="V12" t="n">
+      <c r="AH12" t="n">
         <v>0.1033088360830216</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AI12" t="n">
         <v>0.2782903007973467</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AJ12" t="n">
         <v>0.5066266466725204</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AK12" t="n">
         <v>0.2797288614437856</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AL12" t="n">
         <v>0.4311731532022386</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AM12" t="n">
         <v>0.1762260664248664</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AN12" t="n">
         <v>0.5927265778370958</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AO12" t="n">
         <v>0.1536976889393744</v>
       </c>
-      <c r="AD12" t="n">
-        <v>2.445095253170899</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.910462075411492</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.57567328873338</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.3642317300604844</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.896927003453982</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.116842633215244</v>
+      <c r="AP12" t="n">
+        <v>4.641320305893716</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6.377063590008582</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.615606305253512</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.445095253170918</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.910462075411502</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.575673288733363</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.3642317300604871</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.896927003453964</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.116842633215224</v>
       </c>
     </row>
     <row r="13">
@@ -1787,105 +2357,150 @@
         <v>48</v>
       </c>
       <c r="B13" t="n">
-        <v>0.9931591043404375</v>
+        <v>1.468601253676458</v>
       </c>
       <c r="C13" t="n">
-        <v>0.450920798292604</v>
+        <v>0.9931591043404309</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9239909537445408</v>
+        <v>1.152145918512589</v>
       </c>
       <c r="E13" t="n">
-        <v>1.076828975458541</v>
+        <v>0.450920798292595</v>
       </c>
       <c r="F13" t="n">
-        <v>0.69672388232275</v>
+        <v>10.17002165442115</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6011074563165163</v>
+        <v>0.9239909537445463</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6487325466499838</v>
+        <v>8.334876197400003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3898540095419174</v>
+        <v>1.076828975458546</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2238376262087918</v>
+        <v>2.383610371342153</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2917858601542634</v>
+        <v>0.6967238823227472</v>
       </c>
       <c r="L13" t="n">
-        <v>1.225878614939677</v>
+        <v>1.886730657065258</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6005504559714298</v>
+        <v>0.6011074563165116</v>
       </c>
       <c r="N13" t="n">
-        <v>1.066491459011842</v>
+        <v>1.654394985164826</v>
       </c>
       <c r="O13" t="n">
-        <v>2.0242104939851</v>
+        <v>0.6487325466499766</v>
       </c>
       <c r="P13" t="n">
-        <v>4.491161242232088</v>
+        <v>1.975630732796187</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.554384832727915</v>
+        <v>0.3898540095419198</v>
       </c>
       <c r="R13" t="n">
-        <v>5.88793511021635</v>
+        <v>2.373428611096007</v>
       </c>
       <c r="S13" t="n">
-        <v>4.00950953036206</v>
+        <v>0.2238376262088012</v>
       </c>
       <c r="T13" t="n">
+        <v>2.901111917786293</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.2917858601542647</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4.088128076357497</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.225878614939685</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.523096079562539</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.6005504559714291</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.492422442519621</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.066491459011856</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.884532458697742</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.024210493985109</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.226958648221586</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>4.491161242232094</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0.1547713025258305</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AG13" t="n">
         <v>0.1615350193338242</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AH13" t="n">
         <v>0.09841299377276866</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AI13" t="n">
         <v>0.108185617012529</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AJ13" t="n">
         <v>0.2065589829962158</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AK13" t="n">
         <v>0.1442378959996754</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AL13" t="n">
         <v>0.3785995304101712</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AM13" t="n">
         <v>0.2890573746718144</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AN13" t="n">
         <v>0.3336044543956355</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AO13" t="n">
         <v>0.2362043225983029</v>
       </c>
-      <c r="AD13" t="n">
-        <v>2.657172319062894</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.8937175861119826</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.140299778789468</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.6728952865778414</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.479286707026217</v>
-      </c>
-      <c r="AI13" t="n">
+      <c r="AP13" t="n">
+        <v>3.554384832727907</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>5.887935110216331</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.009509530362093</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.65717231906289</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.8937175861119948</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.14029977878942</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.6728952865778183</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.479286707026186</v>
+      </c>
+      <c r="AX13" t="n">
         <v>2.838092379109201</v>
       </c>
     </row>
@@ -1894,106 +2509,151 @@
         <v>52</v>
       </c>
       <c r="B14" t="n">
-        <v>1.082256433711613</v>
+        <v>1.356959565595839</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3343572263345717</v>
+        <v>1.082256433711612</v>
       </c>
       <c r="D14" t="n">
-        <v>1.555019244614195</v>
+        <v>1.228580082023925</v>
       </c>
       <c r="E14" t="n">
-        <v>1.607497053700762</v>
+        <v>0.3343572263345805</v>
       </c>
       <c r="F14" t="n">
-        <v>1.06840233584448</v>
+        <v>9.878347977879809</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7080639069007163</v>
+        <v>1.555019244614197</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7185303009171023</v>
+        <v>6.326943471432345</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5777716764422692</v>
+        <v>1.607497053700761</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5094441803773764</v>
+        <v>1.970743286200104</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1351699254413067</v>
+        <v>1.068402335844469</v>
       </c>
       <c r="L14" t="n">
-        <v>1.729845568398676</v>
+        <v>1.492487220438168</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4780525390161895</v>
+        <v>0.7080639069007177</v>
       </c>
       <c r="N14" t="n">
-        <v>0.986788184887514</v>
+        <v>1.379308978714133</v>
       </c>
       <c r="O14" t="n">
-        <v>2.059513980436545</v>
+        <v>0.7185303009171073</v>
       </c>
       <c r="P14" t="n">
-        <v>4.614961230626903</v>
+        <v>1.885570479199012</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.143147021972886</v>
+        <v>0.5777716764422597</v>
       </c>
       <c r="R14" t="n">
-        <v>5.126959626663654</v>
+        <v>1.814242107817749</v>
       </c>
       <c r="S14" t="n">
-        <v>5.485312627041038</v>
+        <v>0.5094441803773642</v>
       </c>
       <c r="T14" t="n">
+        <v>2.771185036178917</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.1351699254413097</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.989931188408273</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.729845568398668</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.878623067800119</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4780525390161852</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.317308461917928</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.9867881848875095</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.909870996547828</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.059513980436536</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.145244253663848</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>4.614961230626895</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0.1849703339236144</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AG14" t="n">
         <v>0.1012217972437908</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AH14" t="n">
         <v>0.3036392984433322</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AI14" t="n">
         <v>0.1386194312123039</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AJ14" t="n">
         <v>0.2564354230910302</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AK14" t="n">
         <v>0.117585939064842</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AL14" t="n">
         <v>0.3818187836652195</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AM14" t="n">
         <v>0.1697230960270513</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AN14" t="n">
         <v>0.2023046583872331</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AO14" t="n">
         <v>0.1658413505908727</v>
       </c>
-      <c r="AD14" t="n">
-        <v>2.904938277143557</v>
-      </c>
-      <c r="AE14" t="n">
+      <c r="AP14" t="n">
+        <v>2.14314702197292</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>5.126959626663662</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>5.485312627041004</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.904938277143526</v>
+      </c>
+      <c r="AT14" t="n">
         <v>1.283055093272202</v>
       </c>
-      <c r="AF14" t="n">
-        <v>2.014530496698077</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.262168488255459</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>3.81904689906695</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.188285616029588</v>
+      <c r="AU14" t="n">
+        <v>2.014530496698098</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.262168488255461</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3.819046899066965</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.188285616029579</v>
       </c>
     </row>
     <row r="15">
@@ -2001,106 +2661,151 @@
         <v>56</v>
       </c>
       <c r="B15" t="n">
-        <v>0.9994840599979684</v>
+        <v>0.9593450178844699</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5474140058681932</v>
+        <v>0.9994840599979703</v>
       </c>
       <c r="D15" t="n">
-        <v>1.378824459040049</v>
+        <v>1.313331415142158</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8586737772236601</v>
+        <v>0.5474140058681999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.807210291298517</v>
+        <v>7.435231507859912</v>
       </c>
       <c r="G15" t="n">
-        <v>1.013082480237396</v>
+        <v>1.378824459040047</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8036818309415278</v>
+        <v>3.748435028153136</v>
       </c>
       <c r="I15" t="n">
-        <v>0.723109608548449</v>
+        <v>0.8586737772236578</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6683518722451927</v>
+        <v>1.547066281927794</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1081828975987657</v>
+        <v>1.807210291298523</v>
       </c>
       <c r="L15" t="n">
-        <v>1.600541762616545</v>
+        <v>1.435350916804808</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5623854228149067</v>
+        <v>1.013082480237407</v>
       </c>
       <c r="N15" t="n">
-        <v>1.147110639723515</v>
+        <v>1.314855996131966</v>
       </c>
       <c r="O15" t="n">
-        <v>2.176089113621766</v>
+        <v>0.803681830941538</v>
       </c>
       <c r="P15" t="n">
-        <v>5.056048695988999</v>
+        <v>1.797991411632955</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.856974136367191</v>
+        <v>0.723109608548438</v>
       </c>
       <c r="R15" t="n">
-        <v>2.742824446183775</v>
+        <v>1.719685143163533</v>
       </c>
       <c r="S15" t="n">
-        <v>5.906354296878378</v>
+        <v>0.6683518722451899</v>
       </c>
       <c r="T15" t="n">
+        <v>2.939143113950788</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.1081828975987563</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3.807927233469331</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.600541762616538</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4.790923091695921</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5623854228149057</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.345660997068942</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.147110639723512</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.396272063546591</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.176089113621759</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.301395479921406</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>5.056048695988991</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0.1707399760382849</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AG15" t="n">
         <v>0.06196401156804915</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AH15" t="n">
         <v>0.3101514815464894</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AI15" t="n">
         <v>0.1859590425233541</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AJ15" t="n">
         <v>0.177040068587216</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AK15" t="n">
         <v>0.1582098406442015</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AL15" t="n">
         <v>0.3158484984660606</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AM15" t="n">
         <v>0.13179655236603</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AN15" t="n">
         <v>0.329140368345472</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AO15" t="n">
         <v>0.06153348231637706</v>
       </c>
-      <c r="AD15" t="n">
-        <v>2.111843716186606</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.431242048045093</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>3.167576110525825</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.091554501642976</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.983282729157421</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2.201881845775482</v>
+      <c r="AP15" t="n">
+        <v>2.856974136367169</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.742824446183767</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>5.906354296878408</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.11184371618662</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.431242048045074</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.16757611052585</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.091554501642973</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.983282729157451</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>2.201881845775492</v>
       </c>
     </row>
     <row r="16">
@@ -2108,106 +2813,151 @@
         <v>60</v>
       </c>
       <c r="B16" t="n">
-        <v>1.941621749979443</v>
+        <v>1.226963915448348</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5768059216135665</v>
+        <v>1.941621749979435</v>
       </c>
       <c r="D16" t="n">
-        <v>1.08684606048703</v>
+        <v>1.4949394840181</v>
       </c>
       <c r="E16" t="n">
-        <v>0.933901821722411</v>
+        <v>0.5768059216135671</v>
       </c>
       <c r="F16" t="n">
-        <v>1.55906572191371</v>
+        <v>5.353225541179429</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9566239768015589</v>
+        <v>1.086846060487033</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9069469069057926</v>
+        <v>2.345230892190518</v>
       </c>
       <c r="I16" t="n">
-        <v>1.078530988632947</v>
+        <v>0.9339018217224118</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8962063010273685</v>
+        <v>1.528665669552324</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2494181111563331</v>
+        <v>1.559065721913702</v>
       </c>
       <c r="L16" t="n">
-        <v>1.967348059698001</v>
+        <v>1.493657215155169</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7034616009311444</v>
+        <v>0.9566239768015532</v>
       </c>
       <c r="N16" t="n">
-        <v>1.412777989578095</v>
+        <v>1.409497062735813</v>
       </c>
       <c r="O16" t="n">
-        <v>2.357330120185728</v>
+        <v>0.9069469069057897</v>
       </c>
       <c r="P16" t="n">
-        <v>5.24500442840734</v>
+        <v>1.670488862436223</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.01376447597799</v>
+        <v>1.078530988632948</v>
       </c>
       <c r="R16" t="n">
-        <v>3.078976936102964</v>
+        <v>1.428282799482969</v>
       </c>
       <c r="S16" t="n">
-        <v>11.1600639113811</v>
+        <v>0.8962063010273806</v>
       </c>
       <c r="T16" t="n">
+        <v>3.106514194672416</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.2494181111563337</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3.661275689036674</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.967348059698012</v>
+      </c>
+      <c r="X16" t="n">
+        <v>5.007915917127884</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.7034616009311468</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.111187883092821</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.4127779895781</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.713244616743138</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.357330120185735</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.492436778939801</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>5.245004428407349</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0.1258254126813534</v>
       </c>
-      <c r="U16" t="n">
+      <c r="AG16" t="n">
         <v>0.1575937432048823</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AH16" t="n">
         <v>0.1686279135327572</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AI16" t="n">
         <v>0.1722642129507403</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AJ16" t="n">
         <v>0.1970066517635052</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AK16" t="n">
         <v>0.2251741678382999</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AL16" t="n">
         <v>0.1555875824018916</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AM16" t="n">
         <v>0.1902963993445581</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AN16" t="n">
         <v>0.2784513881071228</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AO16" t="n">
         <v>0.2081638517554925</v>
       </c>
-      <c r="AD16" t="n">
-        <v>0.7415244437578424</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0.5480620998275846</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0.8183116595705735</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.237026949782276</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.116964520797842</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.986861905361614</v>
+      <c r="AP16" t="n">
+        <v>4.013764475978039</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3.078976936102962</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>11.16006391138111</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.7415244437578675</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.5480620998276132</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.818311659570559</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.237026949782289</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.116964520797859</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>2.986861905361636</v>
       </c>
     </row>
     <row r="17">
@@ -2215,106 +2965,151 @@
         <v>64</v>
       </c>
       <c r="B17" t="n">
-        <v>1.836812292903638</v>
+        <v>1.875420794985086</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4092742747583704</v>
+        <v>1.836812292903643</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4209658830752765</v>
+        <v>1.767846375940538</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7327460560316028</v>
+        <v>0.4092742747583799</v>
       </c>
       <c r="F17" t="n">
-        <v>1.24646246678629</v>
+        <v>3.924192550147894</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6515614918042331</v>
+        <v>0.4209658830752764</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4679030962517044</v>
+        <v>2.314181512292096</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9911830985697005</v>
+        <v>0.7327460560315999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7683163238320664</v>
+        <v>1.339783408269181</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5277314621983951</v>
+        <v>1.246462466786288</v>
       </c>
       <c r="L17" t="n">
-        <v>2.170283264407881</v>
+        <v>1.447358939628986</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7547063812364957</v>
+        <v>0.6515614918042364</v>
       </c>
       <c r="N17" t="n">
-        <v>1.480161742139835</v>
+        <v>1.359443166109209</v>
       </c>
       <c r="O17" t="n">
+        <v>0.4679030962517015</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.840177083507872</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.9911830985696896</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.620772968256815</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.7683163238320729</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.672049150912647</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.5277314621983905</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3.570507085941534</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.170283264407885</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.835866626126818</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.7547063812365005</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.9591621114480415</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.480161742139848</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.999945063604098</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.221510426858711</v>
       </c>
-      <c r="P17" t="n">
-        <v>5.101666007598748</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.535510432003073</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4.150563339240666</v>
-      </c>
-      <c r="S17" t="n">
-        <v>6.531875615045811</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="AD17" t="n">
+        <v>4.394291041675422</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>5.101666007598746</v>
+      </c>
+      <c r="AF17" t="n">
         <v>0.2047099634869918</v>
       </c>
-      <c r="U17" t="n">
+      <c r="AG17" t="n">
         <v>0.2707226027017534</v>
       </c>
-      <c r="V17" t="n">
+      <c r="AH17" t="n">
         <v>0.415292731933172</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AI17" t="n">
         <v>0.3021770359203588</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AJ17" t="n">
         <v>0.3681691574036968</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AK17" t="n">
         <v>0.2439701138306165</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AL17" t="n">
         <v>0.1051022948353209</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AM17" t="n">
         <v>0.09602934895851711</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AN17" t="n">
         <v>0.4051832651363134</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AO17" t="n">
         <v>0.2076770612279281</v>
       </c>
-      <c r="AD17" t="n">
-        <v>1.732427258024514</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.097706749107373</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.293381367933525</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.976914981636419</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>4.219328120004755</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.676443564032608</v>
+      <c r="AP17" t="n">
+        <v>3.535510432003097</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>4.150563339240643</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>6.531875615045869</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.732427258024508</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.097706749107392</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.293381367933528</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.976914981636407</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.219328120004765</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>2.676443564032613</v>
       </c>
     </row>
     <row r="18">
@@ -2322,106 +3117,151 @@
         <v>68</v>
       </c>
       <c r="B18" t="n">
-        <v>0.7203115855893309</v>
+        <v>8.806056327370005</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6004314140837689</v>
+        <v>0.7203115855893256</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9502397065232782</v>
+        <v>1.949521437054971</v>
       </c>
       <c r="E18" t="n">
-        <v>1.445031607515982</v>
+        <v>0.6004314140837734</v>
       </c>
       <c r="F18" t="n">
-        <v>1.522885728161858</v>
+        <v>2.842786937434982</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9854161667395069</v>
+        <v>0.9502397065232745</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6361324571413601</v>
+        <v>1.865511080652178</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8251542704831923</v>
+        <v>1.445031607515986</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6533797115153266</v>
+        <v>1.02115424972888</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4417756667332053</v>
+        <v>1.52288572816186</v>
       </c>
       <c r="L18" t="n">
-        <v>1.540459945885856</v>
+        <v>1.302172799075472</v>
       </c>
       <c r="M18" t="n">
-        <v>0.651331209851114</v>
+        <v>0.9854161667395094</v>
       </c>
       <c r="N18" t="n">
-        <v>1.326998140084924</v>
+        <v>1.342922699653051</v>
       </c>
       <c r="O18" t="n">
-        <v>2.212815711934276</v>
+        <v>0.6361324571413546</v>
       </c>
       <c r="P18" t="n">
-        <v>5.071320499163168</v>
+        <v>1.909767034404077</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.501337738480581</v>
+        <v>0.8251542704831958</v>
       </c>
       <c r="R18" t="n">
-        <v>3.905805854440322</v>
+        <v>1.513066022904904</v>
       </c>
       <c r="S18" t="n">
-        <v>9.932492330567866</v>
+        <v>0.6533797115153231</v>
       </c>
       <c r="T18" t="n">
+        <v>2.785770126337127</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.441775666733205</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.914252559126716</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.540459945885864</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.634580715129765</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6513312098511143</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.8786591548227828</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.326998140084926</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.427972834439937</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.212815711934275</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.939650020908332</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>5.071320499163171</v>
+      </c>
+      <c r="AF18" t="n">
         <v>0.4713575613993674</v>
       </c>
-      <c r="U18" t="n">
+      <c r="AG18" t="n">
         <v>0.02910581573430281</v>
       </c>
-      <c r="V18" t="n">
+      <c r="AH18" t="n">
         <v>0.6017362179021415</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AI18" t="n">
         <v>0.1271190822076045</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AJ18" t="n">
         <v>0.3232792398738114</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AK18" t="n">
         <v>0.4120931575395703</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AL18" t="n">
         <v>0.1273127806601086</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AM18" t="n">
         <v>0.1748052888639518</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AN18" t="n">
         <v>0.1648390531014677</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AO18" t="n">
         <v>0.3866094246360468</v>
       </c>
-      <c r="AD18" t="n">
-        <v>1.635289762983733</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.534545898335351</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>3.98869606431326</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.127136907140737</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>4.471081858840765</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.962567571041643</v>
+      <c r="AP18" t="n">
+        <v>6.501337738480554</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>3.905805854440327</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>9.932492330567873</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.635289762983748</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.534545898335337</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.988696064313249</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.127136907140736</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.471081858840767</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>2.962567571041645</v>
       </c>
     </row>
     <row r="19">
@@ -2429,105 +3269,150 @@
         <v>72</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1897378636699098</v>
+        <v>34.02926413374243</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2941033671542625</v>
+        <v>0.1897378636699118</v>
       </c>
       <c r="D19" t="n">
-        <v>1.867281852054455</v>
+        <v>1.782564533315549</v>
       </c>
       <c r="E19" t="n">
-        <v>1.928290467974995</v>
+        <v>0.2941033671542623</v>
       </c>
       <c r="F19" t="n">
-        <v>1.456564528145845</v>
+        <v>3.201695008322631</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8482257642686158</v>
+        <v>1.867281852054451</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6497573712622946</v>
+        <v>2.293492902418176</v>
       </c>
       <c r="I19" t="n">
-        <v>1.046143341231477</v>
+        <v>1.928290467974996</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6042106752578941</v>
+        <v>1.7669265459993</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9286204597417</v>
+        <v>1.45656452814584</v>
       </c>
       <c r="L19" t="n">
-        <v>0.970554648923682</v>
+        <v>1.74044470082366</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3418270312714844</v>
+        <v>0.8482257642686122</v>
       </c>
       <c r="N19" t="n">
-        <v>1.259646844941925</v>
+        <v>1.590396220460785</v>
       </c>
       <c r="O19" t="n">
-        <v>1.971629185935537</v>
+        <v>0.6497573712622859</v>
       </c>
       <c r="P19" t="n">
-        <v>4.947475198599829</v>
+        <v>1.95101398688479</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.645454926261939</v>
+        <v>1.046143341231473</v>
       </c>
       <c r="R19" t="n">
-        <v>8.330466191371697</v>
+        <v>1.52074104041727</v>
       </c>
       <c r="S19" t="n">
-        <v>12.34848414921032</v>
+        <v>0.6042106752578903</v>
       </c>
       <c r="T19" t="n">
+        <v>2.7252797202957</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.9286204597417059</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.701735755455193</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.9705546489236858</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.946931656780469</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.34182703127148</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.8953174518244257</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.259646844941923</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.242203341327523</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.971629185935529</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.364330416154618</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>4.947475198599828</v>
+      </c>
+      <c r="AF19" t="n">
         <v>0.1574087750230844</v>
       </c>
-      <c r="U19" t="n">
+      <c r="AG19" t="n">
         <v>0.4303606415558953</v>
       </c>
-      <c r="V19" t="n">
+      <c r="AH19" t="n">
         <v>0.2103964961871031</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AI19" t="n">
         <v>0.3379526867017642</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AJ19" t="n">
         <v>0.4972673770592373</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AK19" t="n">
         <v>0.1808644485354184</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AL19" t="n">
         <v>0.2880004498696285</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AM19" t="n">
         <v>0.2410946840615036</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AN19" t="n">
         <v>0.3970581619780008</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AO19" t="n">
         <v>0.1595641579322803</v>
       </c>
-      <c r="AD19" t="n">
-        <v>1.541492421390161</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.353447246520943</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.25473232219175</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.897719581592149</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.885593264063729</v>
-      </c>
-      <c r="AI19" t="n">
+      <c r="AP19" t="n">
+        <v>2.645454926261931</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8.33046619137173</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>12.34848414921034</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.54149242139015</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.35344724652094</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.254732322191731</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.897719581592159</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.885593264063721</v>
+      </c>
+      <c r="AX19" t="n">
         <v>4.681227211969598</v>
       </c>
     </row>
@@ -2536,106 +3421,151 @@
         <v>76</v>
       </c>
       <c r="B20" t="n">
-        <v>0.4923262593931524</v>
+        <v>34.63723480638933</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6387174922879505</v>
+        <v>0.492326259393158</v>
       </c>
       <c r="D20" t="n">
-        <v>2.064839012836975</v>
+        <v>1.914491579239453</v>
       </c>
       <c r="E20" t="n">
-        <v>1.948786480421931</v>
+        <v>0.6387174922879529</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9193160732130358</v>
+        <v>2.966138080492481</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6526815018503844</v>
+        <v>2.064839012836983</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4440772177144989</v>
+        <v>2.765138090001544</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7657093223422565</v>
+        <v>1.948786480421938</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5339051238901785</v>
+        <v>1.890483950128479</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9872498207137478</v>
+        <v>0.9193160732130413</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9133141446499428</v>
+        <v>1.900571464187101</v>
       </c>
       <c r="M20" t="n">
-        <v>0.408810016946672</v>
+        <v>0.6526815018503825</v>
       </c>
       <c r="N20" t="n">
-        <v>1.064008169470776</v>
+        <v>1.702847869948263</v>
       </c>
       <c r="O20" t="n">
-        <v>1.895377465129288</v>
+        <v>0.4440772177144948</v>
       </c>
       <c r="P20" t="n">
-        <v>4.754088676569447</v>
+        <v>1.811064988385767</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.168490324188943</v>
+        <v>0.7657093223422544</v>
       </c>
       <c r="R20" t="n">
-        <v>6.114209859286855</v>
+        <v>1.58809131714893</v>
       </c>
       <c r="S20" t="n">
-        <v>10.12741306363474</v>
+        <v>0.5339051238901719</v>
       </c>
       <c r="T20" t="n">
+        <v>2.67733969886943</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.9872498207137373</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.714418591131547</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.9133141446499445</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.354728578276893</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.4088100169466728</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.101434339183053</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.064008169470781</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.131568449261357</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.895377465129295</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.944982236898622</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>4.754088676569457</v>
+      </c>
+      <c r="AF20" t="n">
         <v>0.424590366422226</v>
       </c>
-      <c r="U20" t="n">
+      <c r="AG20" t="n">
         <v>0.2026179015369394</v>
       </c>
-      <c r="V20" t="n">
+      <c r="AH20" t="n">
         <v>0.2729528771639321</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AI20" t="n">
         <v>0.2464293722605313</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AJ20" t="n">
         <v>0.3075372843892237</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AK20" t="n">
         <v>0.3201461539792358</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AL20" t="n">
         <v>0.4176638098238532</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AM20" t="n">
         <v>0.1226242325397029</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AN20" t="n">
         <v>0.3712645914241028</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AO20" t="n">
         <v>0.1072949760977725</v>
       </c>
-      <c r="AD20" t="n">
-        <v>3.329767799302186</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0.9171259385983892</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.195404133617439</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0.8048332942163986</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>6.116811262208946</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.68751059552467</v>
+      <c r="AP20" t="n">
+        <v>5.168490324188978</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>6.114209859286816</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>10.1274130636347</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3.329767799302193</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.91712593859836</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.195404133617469</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.8048332942163999</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>6.116811262208955</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.687510595524643</v>
       </c>
     </row>
     <row r="21">
@@ -2643,106 +3573,151 @@
         <v>80</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2619137059769585</v>
+        <v>33.93464076488825</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7461761612785008</v>
+        <v>0.2619137059769571</v>
       </c>
       <c r="D21" t="n">
-        <v>2.655440235502581</v>
+        <v>1.842429407953355</v>
       </c>
       <c r="E21" t="n">
-        <v>2.200949825176538</v>
+        <v>0.7461761612785019</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8781760456843357</v>
+        <v>4.078574752646802</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8453766304020063</v>
+        <v>2.655440235502578</v>
       </c>
       <c r="H21" t="n">
-        <v>0.518255605203028</v>
+        <v>3.714581564412669</v>
       </c>
       <c r="I21" t="n">
-        <v>1.095240974645273</v>
+        <v>2.20094982517654</v>
       </c>
       <c r="J21" t="n">
-        <v>1.110132185733028</v>
+        <v>2.307200970218937</v>
       </c>
       <c r="K21" t="n">
-        <v>0.906142274808076</v>
+        <v>0.8781760456843354</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5501203713586359</v>
+        <v>2.186598211456244</v>
       </c>
       <c r="M21" t="n">
-        <v>1.153915333052245</v>
+        <v>0.8453766304020089</v>
       </c>
       <c r="N21" t="n">
-        <v>1.258230430759319</v>
+        <v>1.996021164769266</v>
       </c>
       <c r="O21" t="n">
-        <v>2.199006230061206</v>
+        <v>0.5182556052030166</v>
       </c>
       <c r="P21" t="n">
-        <v>4.852986036885541</v>
+        <v>1.738296109654322</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.203842381513139</v>
+        <v>1.095240974645268</v>
       </c>
       <c r="R21" t="n">
-        <v>6.833906751376222</v>
+        <v>2.178919536233142</v>
       </c>
       <c r="S21" t="n">
-        <v>5.594583325678493</v>
+        <v>1.110132185733029</v>
       </c>
       <c r="T21" t="n">
+        <v>2.347510708010143</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.9061422748080784</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3.165419070021962</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.5501203713586381</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4.750658271530943</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.15391533305225</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.684537235757975</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.258230430759325</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.7746233139962946</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.199006230061213</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.415105339403229</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>4.852986036885544</v>
+      </c>
+      <c r="AF21" t="n">
         <v>0.272349159876522</v>
       </c>
-      <c r="U21" t="n">
+      <c r="AG21" t="n">
         <v>0.2881899478168307</v>
       </c>
-      <c r="V21" t="n">
+      <c r="AH21" t="n">
         <v>0.4588520233885577</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AI21" t="n">
         <v>0.1136502117070192</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AJ21" t="n">
         <v>0.2691965241239032</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AK21" t="n">
         <v>0.4223549151267002</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AL21" t="n">
         <v>0.299195457145525</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AM21" t="n">
         <v>0.1151980026428811</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AN21" t="n">
         <v>0.2970664979810266</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AO21" t="n">
         <v>0.255765709770875</v>
       </c>
-      <c r="AD21" t="n">
-        <v>1.553745729752288</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.823684938701743</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.747654659615414</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.818655116358095</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.741341717259086</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>4.324674588293051</v>
+      <c r="AP21" t="n">
+        <v>9.203842381513141</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>6.833906751376225</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>5.594583325678514</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.553745729752247</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.823684938701747</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.747654659615425</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.818655116358109</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.741341717259035</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>4.324674588293047</v>
       </c>
     </row>
     <row r="22">
@@ -2750,106 +3725,151 @@
         <v>84</v>
       </c>
       <c r="B22" t="n">
-        <v>0.6123845871157856</v>
+        <v>34.66131891769955</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6613014629923302</v>
+        <v>0.6123845871157731</v>
       </c>
       <c r="D22" t="n">
-        <v>2.392948219766151</v>
+        <v>1.800833587759227</v>
       </c>
       <c r="E22" t="n">
-        <v>1.829938053137028</v>
+        <v>0.6613014629923221</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8439703048856736</v>
+        <v>4.159876544630647</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5430306791676605</v>
+        <v>2.392948219766143</v>
       </c>
       <c r="H22" t="n">
-        <v>0.469370594137571</v>
+        <v>4.761645403766995</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6233390610228918</v>
+        <v>1.829938053137029</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8201708764945694</v>
+        <v>3.053201210757678</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7490267589055517</v>
+        <v>0.8439703048856746</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9181547923638171</v>
+        <v>2.679578125698027</v>
       </c>
       <c r="M22" t="n">
-        <v>1.064976249359454</v>
+        <v>0.5430306791676627</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9352515061071062</v>
+        <v>2.454610866627495</v>
       </c>
       <c r="O22" t="n">
-        <v>1.929433641778541</v>
+        <v>0.4693705941375795</v>
       </c>
       <c r="P22" t="n">
-        <v>4.536750424042717</v>
+        <v>2.205585221193946</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.429758711510397</v>
+        <v>0.6233390610228903</v>
       </c>
       <c r="R22" t="n">
-        <v>8.59327823053364</v>
+        <v>2.152190388651252</v>
       </c>
       <c r="S22" t="n">
-        <v>10.75812151484984</v>
+        <v>0.8201708764945705</v>
       </c>
       <c r="T22" t="n">
+        <v>3.051645172062116</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.7490267589055601</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3.547572734983081</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.9181547923638196</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.793402550164439</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.064976249359455</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.737903825461378</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.9352515061070964</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9004864718729406</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.929433641778526</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.934759073158747</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>4.536750424042713</v>
+      </c>
+      <c r="AF22" t="n">
         <v>0.1909311072321172</v>
       </c>
-      <c r="U22" t="n">
+      <c r="AG22" t="n">
         <v>0.3419338455409457</v>
       </c>
-      <c r="V22" t="n">
+      <c r="AH22" t="n">
         <v>0.2282361139122193</v>
       </c>
-      <c r="W22" t="n">
+      <c r="AI22" t="n">
         <v>0.2660719106625037</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AJ22" t="n">
         <v>0.6046249968304201</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AK22" t="n">
         <v>0.05703557579305251</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AL22" t="n">
         <v>0.212414210588044</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AM22" t="n">
         <v>0.3632719514975392</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AN22" t="n">
         <v>0.3408260166608869</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AO22" t="n">
         <v>0.2334629494682245</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AP22" t="n">
+        <v>6.42975871151036</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>8.593278230533642</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>10.75812151484979</v>
+      </c>
+      <c r="AS22" t="n">
         <v>2.58302568702915</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1.105043964008149</v>
-      </c>
-      <c r="AF22" t="n">
+      <c r="AT22" t="n">
+        <v>1.105043964008119</v>
+      </c>
+      <c r="AU22" t="n">
         <v>1.464818504691879</v>
       </c>
-      <c r="AG22" t="n">
-        <v>2.63647397809747</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.637004891363461</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>3.18541337945312</v>
+      <c r="AV22" t="n">
+        <v>2.636473978097484</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.637004891363442</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>3.185413379453104</v>
       </c>
     </row>
     <row r="23">
@@ -2857,106 +3877,151 @@
         <v>88</v>
       </c>
       <c r="B23" t="n">
-        <v>0.4683808505048633</v>
+        <v>34.41188174030825</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5187914835897257</v>
+        <v>0.4683808505048643</v>
       </c>
       <c r="D23" t="n">
+        <v>1.750617526804991</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.5187914835897298</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.683491041831334</v>
+      </c>
+      <c r="G23" t="n">
         <v>8.643517618675578</v>
       </c>
-      <c r="E23" t="n">
-        <v>0.5816702655383972</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.7751795169624885</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.2064169501953999</v>
-      </c>
       <c r="H23" t="n">
-        <v>0.3402706912745277</v>
+        <v>5.251276335082983</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3570403489198099</v>
+        <v>0.5816702655384008</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7769879656022968</v>
+        <v>3.970606267273756</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5369337760419889</v>
+        <v>0.775179516962474</v>
       </c>
       <c r="L23" t="n">
-        <v>1.004083544000776</v>
+        <v>3.34895700640626</v>
       </c>
       <c r="M23" t="n">
-        <v>1.244797663007752</v>
+        <v>0.2064169501953873</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8838109620891976</v>
+        <v>3.127105836174235</v>
       </c>
       <c r="O23" t="n">
-        <v>1.518185956326359</v>
+        <v>0.3402706912745163</v>
       </c>
       <c r="P23" t="n">
-        <v>4.01099993334712</v>
+        <v>2.363529876970019</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.559301895740062</v>
+        <v>0.3570403489198037</v>
       </c>
       <c r="R23" t="n">
-        <v>7.649041336929889</v>
+        <v>2.574577435904425</v>
       </c>
       <c r="S23" t="n">
-        <v>8.159392142244771</v>
+        <v>0.7769879656022964</v>
       </c>
       <c r="T23" t="n">
+        <v>3.542540689853142</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.536933776041991</v>
+      </c>
+      <c r="V23" t="n">
+        <v>3.587552182130856</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.00408354400078</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.579365462244476</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.244797663007753</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.830619194422273</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.8838109620891884</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.287698982385376</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.518185956326362</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.738872938835055</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>4.010999933347116</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0.420669856093019</v>
       </c>
-      <c r="U23" t="n">
+      <c r="AG23" t="n">
         <v>0.2010460946140128</v>
       </c>
-      <c r="V23" t="n">
+      <c r="AH23" t="n">
         <v>0.2164289222791769</v>
       </c>
-      <c r="W23" t="n">
+      <c r="AI23" t="n">
         <v>0.1973382238855609</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AJ23" t="n">
         <v>0.2543106261205762</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AK23" t="n">
         <v>0.2738792313614029</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AL23" t="n">
         <v>0.7315745531337983</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AM23" t="n">
         <v>0.2035265269669156</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AN23" t="n">
         <v>0.466212120797741</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AO23" t="n">
         <v>0.1939641408513578</v>
       </c>
-      <c r="AD23" t="n">
-        <v>1.867216229611521</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.343909737258317</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>4.497401364748022</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.977487485247323</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>5.902164680379628</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.23770639327102</v>
+      <c r="AP23" t="n">
+        <v>5.559301895740049</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.649041336929869</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>8.159392142244741</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.867216229611513</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.343909737258315</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.49740136474803</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.977487485247308</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>5.902164680379622</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>2.237706393271002</v>
       </c>
     </row>
     <row r="24">
@@ -2964,106 +4029,151 @@
         <v>92</v>
       </c>
       <c r="B24" t="n">
-        <v>7.331630125344267</v>
+        <v>49.17286762424972</v>
       </c>
       <c r="C24" t="n">
-        <v>7.754988583702754</v>
+        <v>7.33163012534426</v>
       </c>
       <c r="D24" t="n">
-        <v>0.764018894599752</v>
+        <v>59.19025814442536</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6600893252580871</v>
+        <v>7.754988583702747</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8524423161747354</v>
+        <v>4.407711050349564</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2465319183472373</v>
+        <v>0.7640188945997504</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3398416241899783</v>
+        <v>5.028761365439166</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2620229317159415</v>
+        <v>0.6600893252580787</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4664703853697849</v>
+        <v>4.346072810237095</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6330666092518423</v>
+        <v>0.8524423161747395</v>
       </c>
       <c r="L24" t="n">
-        <v>1.036841341630542</v>
+        <v>3.589597645478407</v>
       </c>
       <c r="M24" t="n">
-        <v>1.256918102482642</v>
+        <v>0.2465319183472398</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8798960008678419</v>
+        <v>3.329222429743673</v>
       </c>
       <c r="O24" t="n">
-        <v>1.660401016909972</v>
+        <v>0.3398416241899952</v>
       </c>
       <c r="P24" t="n">
-        <v>3.769970304138992</v>
+        <v>2.96811996498798</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.038851996817812</v>
+        <v>0.262022931715944</v>
       </c>
       <c r="R24" t="n">
-        <v>5.682832548230289</v>
+        <v>3.137824260503895</v>
       </c>
       <c r="S24" t="n">
-        <v>6.261199499227475</v>
+        <v>0.466470385369795</v>
       </c>
       <c r="T24" t="n">
+        <v>3.288194969146238</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.6330666092518489</v>
+      </c>
+      <c r="V24" t="n">
+        <v>3.487869249150349</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.036841341630538</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.050409070517154</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.256918102482634</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.121124964592392</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.8798960008678417</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.3422853695704</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.660401016909967</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.406299403802256</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>3.769970304138989</v>
+      </c>
+      <c r="AF24" t="n">
         <v>0.3818316501313987</v>
       </c>
-      <c r="U24" t="n">
+      <c r="AG24" t="n">
         <v>0.2002869389447907</v>
       </c>
-      <c r="V24" t="n">
+      <c r="AH24" t="n">
         <v>0.2598613328738511</v>
       </c>
-      <c r="W24" t="n">
+      <c r="AI24" t="n">
         <v>0.04055589630917907</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AJ24" t="n">
         <v>0.209733117988503</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AK24" t="n">
         <v>0.1113166156825161</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AL24" t="n">
         <v>0.4603209071198342</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AM24" t="n">
         <v>0.3723600620295582</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AN24" t="n">
         <v>0.5201136477403555</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AO24" t="n">
         <v>0.2454689531636311</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1.902388941476069</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.771443492247192</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>3.362829092572452</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.967335886943002</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.129378665008454</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>3.706504885816631</v>
+      <c r="AP24" t="n">
+        <v>5.038851996817814</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>5.682832548230283</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>6.261199499227472</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.902388941476045</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.77144349224718</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.362829092572441</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.967335886942993</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.129378665008431</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>3.706504885816618</v>
       </c>
     </row>
     <row r="25">
@@ -3071,106 +4181,151 @@
         <v>96</v>
       </c>
       <c r="B25" t="n">
-        <v>9.451219904265143</v>
+        <v>10.57050598199879</v>
       </c>
       <c r="C25" t="n">
-        <v>7.840419747626608</v>
+        <v>9.451219904265136</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7636155105000348</v>
+        <v>59.67253041059618</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8312004847809821</v>
+        <v>7.84041974762661</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5898332170751669</v>
+        <v>4.521687829369223</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1761127558191285</v>
+        <v>0.7636155105000321</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2720219543853378</v>
+        <v>5.135027461276969</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1550649485476655</v>
+        <v>0.831200484780984</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3974059793748727</v>
+        <v>4.387668561983496</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3961159023132256</v>
+        <v>0.5898332170751658</v>
       </c>
       <c r="L25" t="n">
+        <v>3.474283984187525</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1761127558191304</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.830876068425923</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.2720219543853321</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.966749865358892</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.1550649485476673</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.074243327033068</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.3974059793748754</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.709547222783002</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3961159023132174</v>
+      </c>
+      <c r="V25" t="n">
+        <v>3.498916615823305</v>
+      </c>
+      <c r="W25" t="n">
         <v>1.046106610192062</v>
       </c>
-      <c r="M25" t="n">
-        <v>1.421518549354516</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.114326032248383</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.617710490117207</v>
-      </c>
-      <c r="P25" t="n">
-        <v>3.896247459150886</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5.607122372725883</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3.222280445085121</v>
-      </c>
-      <c r="S25" t="n">
-        <v>5.19906474947376</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="X25" t="n">
+        <v>3.882613776720153</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.421518549354525</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.458348411808764</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.114326032248395</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.99679347576724</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.617710490117224</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.535838754389379</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>3.896247459150891</v>
+      </c>
+      <c r="AF25" t="n">
         <v>0.3684454321090121</v>
       </c>
-      <c r="U25" t="n">
+      <c r="AG25" t="n">
         <v>0.183629532855968</v>
       </c>
-      <c r="V25" t="n">
+      <c r="AH25" t="n">
         <v>0.2653025461001063</v>
       </c>
-      <c r="W25" t="n">
+      <c r="AI25" t="n">
         <v>0.2498485224735637</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AJ25" t="n">
         <v>0.08443383601102314</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AK25" t="n">
         <v>0.2085623809202689</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AL25" t="n">
         <v>0.4916045105578536</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AM25" t="n">
         <v>0.1207829671595273</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AN25" t="n">
         <v>0.2744239131799133</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AO25" t="n">
         <v>0.2628350164133765</v>
       </c>
-      <c r="AD25" t="n">
-        <v>3.396632938037993</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.731345181147116</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.630334251335928</v>
-      </c>
-      <c r="AG25" t="n">
+      <c r="AP25" t="n">
+        <v>5.607122372725859</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>3.222280445085168</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>5.199064749473741</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>3.396632938037972</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.731345181147106</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.630334251335903</v>
+      </c>
+      <c r="AV25" t="n">
         <v>2.405844704135367</v>
       </c>
-      <c r="AH25" t="n">
-        <v>3.4943003895879</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.882274431617601</v>
+      <c r="AW25" t="n">
+        <v>3.494300389587888</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>2.882274431617581</v>
       </c>
     </row>
     <row r="26">
@@ -3178,106 +4333,151 @@
         <v>100</v>
       </c>
       <c r="B26" t="n">
-        <v>7.536301414213314</v>
+        <v>48.90586250120964</v>
       </c>
       <c r="C26" t="n">
-        <v>8.016274125466104</v>
+        <v>7.536301414213313</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9020283654499829</v>
+        <v>29.09772903803582</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9866661055842062</v>
+        <v>8.016274125466101</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6779431525086482</v>
+        <v>4.6916436839742</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4521431201565577</v>
+        <v>0.9020283654499853</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4176573597191604</v>
+        <v>5.223840429483525</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3234870871762215</v>
+        <v>0.9866661055842022</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4966062154181494</v>
+        <v>4.715103353027747</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3872697927289608</v>
+        <v>0.677943152508648</v>
       </c>
       <c r="L26" t="n">
-        <v>1.133955617502646</v>
+        <v>3.311147511234735</v>
       </c>
       <c r="M26" t="n">
+        <v>0.4521431201565598</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.8732742172696</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.4176573597191651</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.874230121875797</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.3234870871762303</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.333478183964009</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.4966062154181533</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.396481684086291</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.3872697927289683</v>
+      </c>
+      <c r="V26" t="n">
+        <v>3.509068932779551</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.133955617502644</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.432887297111027</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.256200365350086</v>
       </c>
-      <c r="N26" t="n">
-        <v>1.178108664007415</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.503023107541966</v>
-      </c>
-      <c r="P26" t="n">
-        <v>3.77153604514274</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>9.109937161473129</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.17109234666373</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.915898330212108</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="Z26" t="n">
+        <v>3.579879219746049</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.17810866400742</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.497510089320393</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.503023107541967</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.507545067961838</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>3.771536045142748</v>
+      </c>
+      <c r="AF26" t="n">
         <v>0.4999575210918699</v>
       </c>
-      <c r="U26" t="n">
+      <c r="AG26" t="n">
         <v>0.238294888613947</v>
       </c>
-      <c r="V26" t="n">
+      <c r="AH26" t="n">
         <v>0.5274098458446485</v>
       </c>
-      <c r="W26" t="n">
+      <c r="AI26" t="n">
         <v>0.4093850848000621</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AJ26" t="n">
         <v>0.3498341621060339</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AK26" t="n">
         <v>0.4157860754561524</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AL26" t="n">
         <v>0.4928833860558793</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AM26" t="n">
         <v>0.1832937676124961</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AN26" t="n">
         <v>0.1735861351080246</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AO26" t="n">
         <v>0.1416315304764765</v>
       </c>
-      <c r="AD26" t="n">
-        <v>3.658147876654406</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.332723042977737</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>3.775872476281468</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.983121197948251</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>6.816825912481284</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>4.426939259834115</v>
+      <c r="AP26" t="n">
+        <v>9.109937161473114</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.171092346663713</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.915898330212144</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>3.658147876654404</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.332723042977696</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.775872476281475</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.983121197948303</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>6.816825912481277</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>4.426939259834128</v>
       </c>
     </row>
   </sheetData>
